--- a/10_Yue_Liu/Sample_Sheet_Yue_Liu.xlsx
+++ b/10_Yue_Liu/Sample_Sheet_Yue_Liu.xlsx
@@ -488,12 +488,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Y_A_1</t>
+          <t>Y_8h_1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>两两对比, 客户要求输出参考其它测序商的报告，我看了一下好像和我们的差不多，差不多的话尽量满足，太花时间的话就算了，我来解释，邮件已转发</t>
+          <t>两两对比, 客户要求输出参考其它测序商的报告，我看了一下好像和我们的差不多，差不多的话尽量满足，太花时间的话就算了，我来解释，邮件已转发 | CORRECTED 2026-07-04: 'A' group was mislabeled — actual identity is MOLM13 cells, 8h post X-ray radiation (client correction). Renamed to '8h'. '16' group = 16h post radiation, renamed to '16h' for clarity. Raw FASTQ files on disk still use original A_1/A_2/A_3 naming (Quote_06102601_YueLiu) — only the Group/documentation label changed, no realignment needed. Integrated with client-provided legacy Control/4h(X-Ray) count matrix from OLD_Count/ (different sequencing batch) to build a Control/4h/8h/16h time course.</t>
         </is>
       </c>
     </row>
@@ -540,12 +540,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Y_A_2</t>
+          <t>Y_8h_2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -588,12 +588,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>8h</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Y_A_3</t>
+          <t>Y_8h_3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -634,12 +634,14 @@
           <t>Yue Liu</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>16</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Y_16_1</t>
+          <t>Y_16h_1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -680,12 +682,14 @@
           <t>Yue Liu</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>16</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Y_16_2</t>
+          <t>Y_16h_2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -726,12 +730,14 @@
           <t>Yue Liu</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>16</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>16h</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Y_16_3</t>
+          <t>Y_16h_3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
